--- a/src/Excelsior.Tests/ColumnAttributeTests.Test.verified.xlsx
+++ b/src/Excelsior.Tests/ColumnAttributeTests.Test.verified.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="DeterministicId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="DeterministicId2"/>
   </sheets>
 </workbook>
 </file>
@@ -42,15 +42,15 @@
     </border>
   </borders>
   <cellXfs count="5">
-    <xf fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0"/>
-    <xf fontId="1" fillId="0" borderId="0" applyFont="1" applyFill="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="0" applyFill="0" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0"/>
+    <xf fontId="1" fillId="0" borderId="0" applyFont="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="0" applyFill="0" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="165" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -58,11 +58,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="30" customWidth="1"/>
   </cols>
   <sheetData>

--- a/src/Excelsior.Tests/ColumnAttributeTests.Test.verified.xlsx
+++ b/src/Excelsior.Tests/ColumnAttributeTests.Test.verified.xlsx
@@ -41,7 +41,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0"/>
     <xf fontId="1" fillId="0" borderId="0" applyFont="1" applyFill="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="0" applyFill="0" applyAlignment="1">
@@ -53,6 +53,7 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="0" applyFill="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="0" applyFill="0"/>
   </cellXfs>
 </styleSheet>
 </file>
@@ -60,7 +61,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="1" max="1" width="15" style="5" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
     <col min="4" max="4" width="30" customWidth="1"/>

--- a/src/Excelsior.Tests/ColumnAttributeTests.Test.verified.xlsx
+++ b/src/Excelsior.Tests/ColumnAttributeTests.Test.verified.xlsx
@@ -129,5 +129,10 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:D3"/>
+  <dataValidations count="1">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" sqref="A2:A3">
+      <formula1>ISNUMBER(A2)</formula1>
+    </dataValidation>
+  </dataValidations>
 </worksheet>
 </file>
--- a/src/Excelsior.Tests/ColumnAttributeTests.Test.verified.xlsx
+++ b/src/Excelsior.Tests/ColumnAttributeTests.Test.verified.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\Excelsior\src\Excelsior.Tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5B3F18B-0411-4C95-83B7-462E811D884F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26245F81-A272-4436-9785-0D5789EA426D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5016" yWindow="3324" windowWidth="30960" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Employee ID</t>
   </si>
@@ -40,13 +40,10 @@
     <t>john@company.com</t>
   </si>
   <si>
-    <t>Jane Smith</t>
+    <t>unknown</t>
   </si>
   <si>
     <t>jane@company.com</t>
-  </si>
-  <si>
-    <t>s</t>
   </si>
 </sst>
 </file>
@@ -105,7 +102,22 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -454,13 +466,11 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2">
-        <v>-1</v>
-      </c>
-      <c r="B3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3" t="s">
         <v>6</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>7</v>
@@ -468,9 +478,22 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:D3" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a number." sqref="A2:A3" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <conditionalFormatting sqref="A2:B3">
+    <cfRule type="containsBlanks" dxfId="1" priority="1">
+      <formula>LEN(TRIM(A2))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D3">
+    <cfRule type="containsBlanks" dxfId="0" priority="3">
+      <formula>LEN(TRIM(D2))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation type="custom" showErrorMessage="1" errorTitle="Invalid value" error="Must be a number." sqref="A2:A3" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>ISNUMBER(A2)</formula1>
+    </dataValidation>
+    <dataValidation type="custom" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." sqref="B2:B3 D2:D3" xr:uid="{00000000-0002-0000-0000-000001000000}">
+      <formula1>LEN(TRIM(B2))&gt;0</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/Excelsior.Tests/ColumnAttributeTests.Test.verified.xlsx
+++ b/src/Excelsior.Tests/ColumnAttributeTests.Test.verified.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="DeterministicId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="DeterministicId3"/>
   </sheets>
 </workbook>
 </file>
@@ -41,7 +41,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0"/>
     <xf fontId="1" fillId="0" borderId="0" applyFont="1" applyFill="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="0" applyFill="0" applyAlignment="1">
@@ -53,14 +53,24 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="0" applyFill="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="0" applyFill="0"/>
   </cellXfs>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="1" max="1" width="15" style="5" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
     <col min="4" max="4" width="30" customWidth="1"/>
@@ -128,5 +138,42 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:D3"/>
+  <conditionalFormatting sqref="A2:A3">
+    <cfRule type="containsBlanks" dxfId="0" priority="1">
+      <formula>LEN(TRIM(A2))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:B3">
+    <cfRule type="containsBlanks" dxfId="0" priority="2">
+      <formula>LEN(TRIM(B2))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D3">
+    <cfRule type="containsBlanks" dxfId="0" priority="3">
+      <formula>LEN(TRIM(D2))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="3">
+    <dataValidation type="custom" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="Must be a number." sqref="A2:A3">
+      <formula1>ISNUMBER(A2)</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." sqref="B2:B3">
+      <formula1>LEN(TRIM(B2))&gt;0</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." sqref="D2:D3">
+      <formula1>LEN(TRIM(D2))&gt;0</formula1>
+    </dataValidation>
+  </dataValidations>
 </worksheet>
+</file>
+
+<file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
+<columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
+  <sheet name="Sheet1">
+    <column index="1" property="Id"/>
+    <column index="2" property="Name"/>
+    <column index="3" property="HireDate"/>
+    <column index="4" property="Email"/>
+  </sheet>
+</columnMetadata>
 </file>
--- a/src/Excelsior.Tests/ColumnAttributeTests.Test.verified.xlsx
+++ b/src/Excelsior.Tests/ColumnAttributeTests.Test.verified.xlsx
@@ -72,7 +72,7 @@
   <cols>
     <col min="1" max="1" width="15" style="5" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="30" customWidth="1"/>
   </cols>
   <sheetData>

--- a/src/Excelsior.Tests/ColumnAttributeTests.Test.verified.xlsx
+++ b/src/Excelsior.Tests/ColumnAttributeTests.Test.verified.xlsx
@@ -70,7 +70,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="1" width="15" style="5" customWidth="1"/>
+    <col min="1" max="1" width="16" style="5" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="30" customWidth="1"/>

--- a/src/Excelsior.Tests/ColumnAttributeTests.Test.verified.xlsx
+++ b/src/Excelsior.Tests/ColumnAttributeTests.Test.verified.xlsx
@@ -70,9 +70,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="1" width="15" style="5" customWidth="1"/>
+    <col min="1" max="1" width="16" style="5" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="30" customWidth="1"/>
   </cols>
   <sheetData>
